--- a/registration_forms/035_workshop_facilitator_application_form--registration_forms.xlsx
+++ b/registration_forms/035_workshop_facilitator_application_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>bi-weekly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Bi-Weekly</t>
         </is>
       </c>
     </row>
@@ -1250,350 +1250,299 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>bi-weekly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bi-Weekly</t>
+          <t>Annual</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>workshop_frequency_choices</t>
+          <t>workshop_location_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bi-monthly</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bi-Monthly</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>workshop_frequency_choices</t>
+          <t>workshop_location_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>off-site</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Off-site</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>workshop_frequency_choices</t>
+          <t>workshop_location_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>on-site</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Annual</t>
+          <t>On-site</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>workshop_location_choices</t>
+          <t>workshop_facilitators_agreed_to_terms_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>workshop_location_choices</t>
+          <t>workshop_facilitators_agreed_to_terms_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>off-site</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Off-site</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>workshop_location_choices</t>
+          <t>workshop_facilitators_agreed_to_part_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>on-site</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>workshop_facilitators_agreed_to_terms_choices</t>
+          <t>workshop_facilitators_agreed_to_part_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>workshop_facilitators_agreed_to_terms_choices</t>
+          <t>workshop_facilitators_reference_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>workshop_facilitators_agreed_to_part_choices</t>
+          <t>workshop_facilitators_reference_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>workshop_facilitators_agreed_to_part_choices</t>
+          <t>workshop_facilitators_agreed_terms_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>workshop_facilitators_reference_choices</t>
+          <t>workshop_facilitators_agreed_terms_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>workshop_facilitators_reference_choices</t>
+          <t>workshop_facilitators_agreed_part_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>workshop_facilitators_agreed_terms_choices</t>
+          <t>workshop_facilitators_agreed_part_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>workshop_facilitators_agreed_terms_choices</t>
+          <t>workshop_facilitators_agreed_reference_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>workshop_facilitators_agreed_part_choices</t>
+          <t>workshop_facilitators_agreed_reference_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>workshop_facilitators_agreed_part_choices</t>
+          <t>workshop_facilitators_agreed_terms_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>workshop_facilitators_agreed_reference_choices</t>
+          <t>workshop_facilitators_agreed_terms_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>workshop_facilitators_agreed_reference_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>workshop_facilitators_agreed_terms_2_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>workshop_facilitators_agreed_terms_2_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
         <is>
           <t>No</t>
         </is>
